--- a/_Master_Data/exclusion.xlsx
+++ b/_Master_Data/exclusion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NSU_2027\Desktop\미국 공급망 고도화\1. 미국 주재원\비전2030(2026)\4.3.2 수요계획 강화\S&amp;OP\DashBoard 개발\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F876A5-A99E-4F36-92B1-52BD385FDC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F3667B-F7C5-4BDC-8CC4-4C5FD17721F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9495" yWindow="2175" windowWidth="17280" windowHeight="9960" xr2:uid="{33A7EF07-1955-4B46-A6FA-45122B72455D}"/>
+    <workbookView xWindow="7785" yWindow="2760" windowWidth="18750" windowHeight="11610" xr2:uid="{33A7EF07-1955-4B46-A6FA-45122B72455D}"/>
   </bookViews>
   <sheets>
     <sheet name="제외품목리스트" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
   <si>
     <t>제품코드</t>
   </si>
@@ -170,22 +170,28 @@
     <t>Shin Ramyun Gold 16 (4x4) CAN</t>
   </si>
   <si>
+    <t>Kimchi Ramyun 16 (4x4) CAN</t>
+  </si>
+  <si>
+    <t>Bowl Noodles Savory Beef 12 CAN</t>
+  </si>
+  <si>
+    <t>Bowl Noodles Savory Chicken 12 CAN</t>
+  </si>
+  <si>
+    <t>Shin Ramyun Black 10 Club</t>
+  </si>
+  <si>
+    <t>(E)K-Ramyun Best 4Mix 16(SOxSBxNSxC)</t>
+  </si>
+  <si>
+    <t>(E)Shin Chapa 2Mix 8(SOxC)</t>
+  </si>
+  <si>
     <t>Chapagetti 16 (4x4) CAN</t>
   </si>
   <si>
     <t>Neoguri Spicy Seafood 10 CAN</t>
-  </si>
-  <si>
-    <t>Kimchi Ramyun 16 (4x4) CAN</t>
-  </si>
-  <si>
-    <t>Bowl Noodles Savory Beef 12 CAN</t>
-  </si>
-  <si>
-    <t>Bowl Noodles Savory Chicken 12 CAN</t>
-  </si>
-  <si>
-    <t>Shin Ramyun Black 10 Club</t>
   </si>
 </sst>
 </file>
@@ -605,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E99EE1D-32AC-4937-AF7B-2CBCECE527B9}">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
@@ -955,10 +961,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32" s="2">
-        <v>101070203</v>
+        <v>101070197</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
         <v>3</v>
@@ -966,10 +972,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33" s="2">
-        <v>101070205</v>
+        <v>101070203</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
         <v>3</v>
@@ -977,10 +983,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34" s="2">
-        <v>101070220</v>
+        <v>101070205</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" t="s">
         <v>3</v>
@@ -988,10 +994,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35" s="2">
-        <v>101070221</v>
+        <v>101070220</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C35" t="s">
         <v>3</v>
@@ -999,54 +1005,54 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A36" s="2">
+        <v>101070221</v>
+      </c>
+      <c r="B36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A37" s="2">
+        <v>101070222</v>
+      </c>
+      <c r="B37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A38" s="2">
         <v>101070224</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B38" t="s">
         <v>38</v>
       </c>
-      <c r="C36" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A37" s="2">
+      <c r="C38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
         <v>101070232</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C37" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="C39" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
         <v>101070233</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="C38" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="2">
-        <v>101004220</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="2">
-        <v>101004256</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="C40" t="s">
         <v>3</v>
@@ -1054,10 +1060,10 @@
     </row>
     <row r="41" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>101004227</v>
+        <v>101004220</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
         <v>3</v>
@@ -1065,10 +1071,10 @@
     </row>
     <row r="42" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>101004240</v>
+        <v>101004256</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C42" t="s">
         <v>3</v>
@@ -1079,7 +1085,7 @@
         <v>101004157</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C43" t="s">
         <v>3</v>
@@ -1090,7 +1096,7 @@
         <v>101070178</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C44" t="s">
         <v>3</v>
@@ -1101,20 +1107,42 @@
         <v>101070177</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C45" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>101070085</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C46" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>101004227</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A48" s="2">
+        <v>101004240</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" t="s">
         <v>3</v>
       </c>
     </row>

--- a/_Master_Data/exclusion.xlsx
+++ b/_Master_Data/exclusion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NSU_2027\Desktop\미국 공급망 고도화\1. 미국 주재원\비전2030(2026)\4.3.2 수요계획 강화\S&amp;OP\DashBoard 개발\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F3667B-F7C5-4BDC-8CC4-4C5FD17721F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0165167-2B72-4E4C-B7B2-8221C02BC8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7785" yWindow="2760" windowWidth="18750" windowHeight="11610" xr2:uid="{33A7EF07-1955-4B46-A6FA-45122B72455D}"/>
+    <workbookView xWindow="5160" yWindow="1695" windowWidth="21000" windowHeight="12390" xr2:uid="{33A7EF07-1955-4B46-A6FA-45122B72455D}"/>
   </bookViews>
   <sheets>
     <sheet name="제외품목리스트" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="52">
   <si>
     <t>제품코드</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>Neoguri Spicy Seafood 10 CAN</t>
+  </si>
+  <si>
+    <t>Shin Cup 3 [KDH-Netflix House]</t>
   </si>
 </sst>
 </file>
@@ -611,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E99EE1D-32AC-4937-AF7B-2CBCECE527B9}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
@@ -807,10 +810,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" s="2">
-        <v>101070129</v>
+        <v>101070119</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
         <v>3</v>
@@ -818,10 +821,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" s="2">
-        <v>101070130</v>
+        <v>101070129</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
         <v>3</v>
@@ -829,10 +832,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" s="2">
-        <v>101070131</v>
+        <v>101070130</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
         <v>3</v>
@@ -840,10 +843,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" s="2">
-        <v>101070132</v>
+        <v>101070131</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
@@ -851,10 +854,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" s="2">
-        <v>101070137</v>
+        <v>101070132</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
         <v>3</v>
@@ -862,10 +865,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23" s="2">
-        <v>101070138</v>
+        <v>101070137</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
         <v>3</v>
@@ -873,10 +876,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24" s="2">
-        <v>101070139</v>
+        <v>101070138</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
         <v>3</v>
@@ -884,10 +887,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25" s="2">
-        <v>101070141</v>
+        <v>101070139</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
         <v>3</v>
@@ -895,10 +898,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26" s="2">
-        <v>101070144</v>
+        <v>101070141</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
         <v>3</v>
@@ -906,10 +909,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27" s="2">
-        <v>101070183</v>
+        <v>101070144</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
         <v>3</v>
@@ -917,10 +920,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28" s="2">
-        <v>101070184</v>
+        <v>101070183</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
         <v>3</v>
@@ -928,10 +931,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29" s="2">
-        <v>101070185</v>
+        <v>101070184</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
         <v>3</v>
@@ -939,10 +942,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30" s="2">
-        <v>101070186</v>
+        <v>101070185</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
         <v>3</v>
@@ -950,10 +953,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31" s="2">
-        <v>101070191</v>
+        <v>101070186</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
         <v>3</v>
@@ -961,10 +964,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32" s="2">
-        <v>101070197</v>
+        <v>101070191</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
         <v>3</v>
@@ -972,10 +975,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33" s="2">
-        <v>101070203</v>
+        <v>101070197</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
         <v>3</v>
@@ -983,10 +986,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34" s="2">
-        <v>101070205</v>
+        <v>101070203</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
         <v>3</v>
@@ -994,10 +997,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35" s="2">
-        <v>101070220</v>
+        <v>101070205</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
         <v>3</v>
@@ -1005,10 +1008,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A36" s="2">
-        <v>101070221</v>
+        <v>101070220</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36" t="s">
         <v>3</v>
@@ -1016,10 +1019,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37" s="2">
-        <v>101070222</v>
+        <v>101070221</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C37" t="s">
         <v>3</v>
@@ -1027,43 +1030,43 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38" s="2">
+        <v>101070222</v>
+      </c>
+      <c r="B38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A39" s="2">
         <v>101070224</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>38</v>
       </c>
-      <c r="C38" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A39" s="2">
+      <c r="C39" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
         <v>101070232</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C39" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="C40" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
         <v>101070233</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B41" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="C40" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="2">
-        <v>101004220</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="C41" t="s">
         <v>3</v>
@@ -1071,10 +1074,10 @@
     </row>
     <row r="42" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>101004256</v>
+        <v>101004220</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" t="s">
         <v>3</v>
@@ -1082,10 +1085,10 @@
     </row>
     <row r="43" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>101004157</v>
+        <v>101004256</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" t="s">
         <v>3</v>
@@ -1093,32 +1096,32 @@
     </row>
     <row r="44" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
+        <v>101004157</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
         <v>101070178</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B45" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C44" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A45" s="2">
+      <c r="C45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A46" s="2">
         <v>101070177</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B46" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="C45" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="2">
-        <v>101070085</v>
-      </c>
-      <c r="B46" t="s">
-        <v>46</v>
       </c>
       <c r="C46" t="s">
         <v>3</v>
@@ -1126,23 +1129,34 @@
     </row>
     <row r="47" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
+        <v>101070085</v>
+      </c>
+      <c r="B47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
         <v>101004227</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B48" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C47" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A48" s="2">
+      <c r="C48" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A49" s="2">
         <v>101004240</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B49" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>3</v>
       </c>
     </row>
